--- a/backtest_runs/20260410_193731/by_symbol/ATLH/ATLH.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/ATLH/ATLH.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -633,7 +633,7 @@
         <v>-2795.480000000009</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>99033.72</v>
@@ -679,7 +679,7 @@
         <v>-10634.51999999999</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>88399.20000000001</v>
@@ -817,7 +817,7 @@
         <v>-1758.480000000009</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>92743.03999999999</v>
@@ -863,7 +863,7 @@
         <v>-118.3200000000006</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>92624.72</v>
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>92624.72</v>
@@ -955,7 +955,7 @@
         <v>-1904</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>90720.72</v>
@@ -1047,7 +1047,7 @@
         <v>-781.3200000000006</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>90537.12</v>
@@ -1185,7 +1185,7 @@
         <v>-629.6799999999994</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>90589.48</v>
@@ -1231,7 +1231,7 @@
         <v>-46.24000000000433</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>90543.23999999999</v>
@@ -1277,7 +1277,7 @@
         <v>-1280.439999999995</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>89262.79999999999</v>
@@ -1415,7 +1415,7 @@
         <v>-858.839999999992</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>98980.68000000001</v>
@@ -1461,7 +1461,7 @@
         <v>-3978</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>95002.68000000001</v>
@@ -1507,7 +1507,7 @@
         <v>-531.0799999999963</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>94471.60000000001</v>
@@ -1645,7 +1645,7 @@
         <v>-408.6799999999994</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>104456.04</v>
